--- a/data/worldcup_0624_0623update.xlsx
+++ b/data/worldcup_0624_0623update.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -458,48 +458,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>官方：摩洛哥裁判贾耶德将执法世界杯葡萄牙vs乌兹别克斯坦</t>
+          <t>Portugal vs Uzbekistan: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-21 01:48</t>
+          <t>2026-06-22T10:01:30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953234.html</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/portugal-vs-uzbekistan-prediction-world-cup-2026-match-preview</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Portugal and Cristiano Ronaldo will be looking to step things up against Uzbekistan after a disappointing World Cup draw with DR Congo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>官方：摩洛哥裁判贾耶德将执法世界杯葡萄牙vs乌兹别克斯坦</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-21 01:48</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953234.html</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Portugal vs Uzbekistan: predictions, best bets, stats and odds</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2 hours ago</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/portugal-vs-uzbekistan-predictions-tips/</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">No previous meetings between these teams.
 No price boosts for this event.
@@ -509,37 +536,10 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 13</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -549,182 +549,186 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sun Jun 21 2026 15:</t>
+          <t>Sun, 21 Jun 2026 13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>卡纳瓦罗：C罗和梅西一样一直是最佳之一，葡萄牙的阵容星光熠熠</t>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>zhibo8</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-22 15:55:00</t>
+          <t>Sun Jun 21 2026 15:</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e9cae7ef0native.htm</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>卡纳瓦罗：C罗和梅西一样一直是最佳之一，葡萄牙的阵容星光熠熠</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:55:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e9cae7ef0native.htm</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-06-21T18:22:43</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
 The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-06-21T17:04:43</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-06-21T16:35:30</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
 The 2026 FIFA World Cup has completely ta</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-06-21T16:11:53</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>武磊：我感觉葡萄牙今年想要拿世界杯冠军还是挺有难度的</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-06-21 23:26</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955601.html</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>世体：葡萄牙世界杯开局低迷，C罗因队内地位引发争议</t>
+          <t>武磊：我感觉葡萄牙今年想要拿世界杯冠军还是挺有难度的</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -734,12 +738,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-21 13:41</t>
+          <t>2026-06-21 23:26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954496.html</t>
+          <t>https://www.dongqiudi.com/articles/5955601.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -747,30 +751,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uzbekistan at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
+          <t>世体：葡萄牙世界杯开局低迷，C罗因队内地位引发争议</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kickoff</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-21 13:41</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://kickoff.guide/blog/uzbekistan-world-cup-2026-guide</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>A team profile of Uzbekistan, who reached a first-ever FIFA World Cup: 50th in the FIFA ranking, coached by Italy's World Cup-winning captain Fabio Ca</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5954496.html</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Portugal at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+          <t>Uzbekistan at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -781,46 +785,42 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://kickoff.guide/blog/portugal-world-cup-2026-guide</t>
+          <t>https://kickoff.guide/blog/uzbekistan-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A team profile of Portugal at the FIFA World Cup 2026: 5th in the FIFA ranking, 9th appearance and seventh in a row, Roberto Martinez's tactics, Crist</t>
+          <t>A team profile of Uzbekistan, who reached a first-ever FIFA World Cup: 50th in the FIFA ranking, coached by Italy's World Cup-winning captain Fabio Ca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Golden Boot: World Cup 2026 top goalscorers</t>
+          <t>Portugal at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Thu, 18 Jun 2026 08</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/golden-boot-world-cup-2026-top-goalscorers-winner</t>
+          <t>https://kickoff.guide/blog/portugal-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Who is winning the battle to be top scorer at the World Cup? Live and updated throughout the tournament  All-time World Cup goalscorers  The Golden Bo</t>
+          <t>A team profile of Portugal at the FIFA World Cup 2026: 5th in the FIFA ranking, 9th appearance and seventh in a row, Roberto Martinez's tactics, Crist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Iran’s Beiranvand denies 10-man Belgium in World Cup draw as Nathan Ngoy sees red</t>
+          <t>Golden Boot: World Cup 2026 top goalscorers</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -830,24 +830,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 21</t>
+          <t>Thu, 18 Jun 2026 08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/belgium-iran-world-cup-group-g-match-report</t>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/golden-boot-world-cup-2026-top-goalscorers-winner</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>There was simply no debate over the moment of the match and it is one that Iran will cherish, even more so if they are to progress to the World Cup kn</t>
+          <t>Who is winning the battle to be top scorer at the World Cup? Live and updated throughout the tournament  All-time World Cup goalscorers  The Golden Bo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
+          <t>Iran’s Beiranvand denies 10-man Belgium in World Cup draw as Nathan Ngoy sees red</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -857,24 +857,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 04</t>
+          <t>Sun, 21 Jun 2026 21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/belgium-iran-world-cup-group-g-match-report</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
+          <t>There was simply no debate over the moment of the match and it is one that Iran will cherish, even more so if they are to progress to the World Cup kn</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Past and present World Cups collide as Beiranvand first gives Iran inspiration, then hope</t>
+          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -884,339 +884,393 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 02</t>
+          <t>Sun, 21 Jun 2026 04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-iran-goalkeeper-alireza-beiranvand</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">The goalkeeper’s 59th-minute save left mouths agape but it’s not the first time he has created an indelible moment for the team  As they prepared for </t>
+          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>World Cup 2026: Can Lionel Messi and Cristiano Ronaldo finally meet on biggest stage?</t>
+          <t>Lionel Messi broke two more World Records vs Austria tonight</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-22T06:43:30</t>
+          <t>Mon, 22 Jun 2026 22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48972466/world-cup-2026-lionel-messi-cristiano-ronaldo-showdown-knockouts-argentina-portugal</t>
+          <t>https://www.fourfourtwo.com/person/player/lionel-messi-broke-two-more-world-records-vs-austria-tonight</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>In a sixth World Cup for Lionel Messi and Cristiano Ronaldo, could the pair finally face each other in the tournament?</t>
+          <t>Argentina’s 2-0 win over Austria took them through to the round of 32 and all but confirmed them as the winners of Group J.  World Cup 2026 has so far</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lamine Yamal shows why this could be his World Cup</t>
+          <t>Past and present World Cups collide as Beiranvand first gives Iran inspiration, then hope</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-21T19:27:01</t>
+          <t>Mon, 22 Jun 2026 02</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cj0gy46d5vro?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-iran-goalkeeper-alireza-beiranvand</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">'He's the main man!' - Rooney on Lamine Yamal  Lamine Yamal was the story before kick-off and is dominating conversation long after the final whistle </t>
+          <t xml:space="preserve">The goalkeeper’s 59th-minute save left mouths agape but it’s not the first time he has created an indelible moment for the team  As they prepared for </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>The World Cup records that look set to be broken</t>
+          <t>World Cup 2026: Can Lionel Messi and Cristiano Ronaldo finally meet on biggest stage?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-21T13:55:05</t>
+          <t>2026-06-22T06:43:30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.espn.com/soccer/story/_/id/48972466/world-cup-2026-lionel-messi-cristiano-ronaldo-showdown-knockouts-argentina-portugal</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+          <t>In a sixth World Cup for Lionel Messi and Cristiano Ronaldo, could the pair finally face each other in the tournament?</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Lamine Yamal shows why this could be his World Cup</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-21T19:27:01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cj0gy46d5vro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'He's the main man!' - Rooney on Lamine Yamal  Lamine Yamal was the story before kick-off and is dominating conversation long after the final whistle </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Most FIFA World Cup Appearances by a Player</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2026-06-20T19:39:34</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/most-world-cup-appearances-by-a-player/</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Here are the players who have combined longevity and excellence to record the most men’s FIFA World Cup appearances of all time.
 Lionel Messi: Argent</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Most Red Cards in World Cup History: Players, Teams and Incidents That Made History</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2026-06-20T19:21:25</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/most-red-cards-in-world-cup-history/</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">From Zinedine Zidane’s headbutt to Wayne Rooney’s stamp, discover which players and teams have received the most red cards in FIFA World Cup history.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>The Oldest Players in World Cup History</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-06-20T19:09:14</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/oldest-players-in-world-cup-history/</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Age is just a number for some footballers. Some even play the game on the grandest stage of all just before the end of their career. Here, we chart th</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>FIFA World Cup Hat-Tricks: The Facts</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-06-19T00:28:32</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/world-cup-hat-tricks-fifa/</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>There have been 56 hat-tricks scored in men’s FIFA World Cup finals tournaments. We give a rundown of the best facts about World Cup hat-tricks, as we</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bracketology: predict a path to World Cup victory</t>
+          <t>The Oldest Players in World Cup History</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 10</t>
+          <t>2026-06-20T19:09:14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+          <t>https://theanalyst.com/articles/oldest-players-in-world-cup-history/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+          <t>Age is just a number for some footballers. Some even play the game on the grandest stage of all just before the end of their career. Here, we chart th</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>FIFA World Cup Hat-Tricks: The Facts</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-19T00:28:32</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/world-cup-hat-tricks-fifa/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>There have been 56 hat-tricks scored in men’s FIFA World Cup finals tournaments. We give a rundown of the best facts about World Cup hat-tricks, as we</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bracketology: predict a path to World Cup victory</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2026-06-22 08:38</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
 对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>How does qualification for the World Cup knockout stage work?</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>2026-06-20T16:24:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Colombia at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>kickoff</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://kickoff.guide/blog/colombia-world-cup-2026-guide</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">A team profile of Colombia (Los Cafeteros) at the FIFA World Cup 2026: 13th in the FIFA ranking, 7th appearance, best result the 2014 quarter-finals, </t>
         </is>
@@ -1233,7 +1287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1298,25 +1352,133 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Thomas Tuchel urges England to improve defence against Ghana after ‘wake-up call’</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/23/thomas-tuchel-england-ghana-world-cup-defence-improve</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Win over Ghana could secure top spot in the group  ‘We dropped too deep,’ Tuchel says of Croatia opener  Thomas Tuchel believes England were given a w</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tuchel’s brash Britpop football is music to England ears before Ghana test</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/23/thomas-tuchel-britpop-football-england-world-cup-ghana</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vinyl has baffled youngsters at the team’s hotel but spells of opening victory against Croatia showed side in the groove  I nside the foyer of the Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Semenyo and Ghana out to emulate 2010 World Cup heroes as they face England</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/antoine-semenyo-ghana-2010-world-cup-team-england</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Carlos Queiroz’s squad hope to repeat the form that almost made Ghana the first African team to reach the semi-finals  A ntoine Semenyo was only 10 ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>England World Cup latest: Thomas Tuchel set to leave it late to name XI to face Ghana on Tuesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/news/12040/13556853/england-world-cup-latest-thomas-tuchel-set-to-leave-it-late-to-name-xi-to-face-ghana-on-tuesday</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sky Sports News' Rob Dorsett explains why Thomas Tuchel delays telling his England players if they are starting and looks at the selection dilemmas th</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>England vs Ghana: predictions, best bets, stats and odds</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>8 minutes ago</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-predictions-betting-tips/</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">No previous meetings between these teams.
 No price boosts for this event.
@@ -1326,105 +1488,348 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>England vs Ghana team news and predicted lineups</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>44 minutes ago</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-team-news-predicted-lineups/</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>England will look to seal their place in the knockout stages when they face Ghana in Group L at the 2026 World Cup on Tuesday. Kick-off is scheduled f</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Who is Saíd Martínez? 'The mathematician' set to referee England vs. Ghana at the World Cup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-22T22:45:49</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49145445/who-said-martinez-england-vs-ghana-2026-world-cup-referee</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>England will look to build on a strong start to their World Cup campaign when they face Ghana in Group L on Tuesday, as victory will see them progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Why Ghana vs. England means more to Antoine Semenyo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-22T22:33:41</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/video/clip/_/id/49147665/why-ghana-vs-england-means-more-antoine-semenyo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Why Ghana vs. England means more to Antoine Semenyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>England vs. Ghana: Kick-off time, team news, how to watch FIFA World Cup clash</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-22T22:27:18</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/espn/story/_/id/49116820/kick-team-news-how-watch-fifa-world-cup-clash</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ghana under Carlos Queiroz have many players who will be a known quantity for England, but the Black Stars pose a threat at the World Cup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Carlos Queiroz says Ghana's '33 million lions' ready for England challenge</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-22T22:08:12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/espn/story/_/id/49146848/carlos-queiroz-says-ghana-33-million-lions-ready-england-challenge</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ghana coach Carlos Queiroz says England may wear three lions on their crest, but his Black Stars carry an entire nation of 33 million lions of their o</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ghana's Thomas Partey 'ready' for England, visa issues 'out of control'</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-22T21:34:56</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49147003/ghana-thomas-partey-ready-england-denied-entry-world-cup-opener</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Thomas Partey has said he is "ready to play" against England on Tuesday after being denied entry to Canada for Ghana's World Cup opener.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ghana's Partey ready to play against England</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-22T19:50:09</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c75y4kqgn1wo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghana midfielder Thomas Partey says he is ready to face England after being denied entry to Canada for the Black Stars' World Cup opener.  The former </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Resolving the Jordan Ayew dilemma and other areas of focus for Ghana vs. England</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-22T19:19:11</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/espn/story/_/id/49142576/resolving-jordan-ayew-dilemma-other-areas-focus-ghana-vs-england</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ghana and England have met only once before at senior level - a 1-1 friendly draw at Wembley in March 2011. Tuesday's match marks their first competit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ghana scouting report: Can Antoine Semenyo and co. shock England?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:41:32</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49108137/ghana-scouting-report-antoine-semenyo-co-shock-england</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>The lowdown on the Black Stars ahead of their group stage encounter against Thomas Tuchel's England.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>England vs Ghana: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-22T10:00:07</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/england-vs-ghana-prediction-world-cup-2026-match-preview</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>England can guarantee their place in the knockout rounds on a potentially momentous day for Harry Kane and Jude Bellingham. Look ahead to England vs G</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Saka trains with England squad before Ghana match</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>2026-06-22T00:13:38</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/c8e21d5w0pjo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Bukayo Saka (right) trained with the England squad on Sunday  Bukayo Saka has trained with the England squad to provide a fitness boost to Thomas Tuch</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>官方：马宁担任英格兰vs加纳第四官员，周飞担任候补助理裁判</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>dongqiudi_team</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>2026-06-21 00:30</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/articles/5953123.html</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>England v Ghana: Live stream, team news, tickets and more</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>2026-06-18T07:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/england-ghana-preview-live-stream-team-news-tickets</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>This is a modal window.
 Europe and Africa go head-to-head at Boston Stadium when England and Ghana meet in their second Group L fixture.
@@ -1432,528 +1837,730 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>From Times Square to England squad: Trevoh Chalobah realises World Cup dream</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 18</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/from-times-square-to-england-squad-trevoh-chalobah-realises-world-cup-dream</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Chelsea defender has mad scramble for boots and cuts short holiday after belatedly receiving the message of a lifetime from Thomas Tuchel  T revoh Cha</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 13</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Thomas Partey in spotlight as he faces England and former Arsenal teammates after rape charges</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 11</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/thomas-partey-england-ghana-handshake</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ghana midfielder has denied all accusations as he prepares to begin his World Cup campaign in Boston on Tuesday  T he Football Association has remaine</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>England offer rare peek behind the curtain with no place to hide under Tuchel</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/england-world-cup-training-intensity-peek-behind-curtain-thomas-tuchel</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">There was more insight at the World Cup training base than usual with intensity on the rise under Thomas Tuchel  T he tall hooded figure kept barking </t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Sun Jun 21 2026 15:</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Women’s T20 World Cup: West Indies defeat Sri Lanka by five wickets to stay unbeaten ahead of crunch England match</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>skysports</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 14</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://www.skysports.com/cricket/news/12040/13556291/womens-t20-world-cup-west-indies-defeat-sri-lanka-by-five-wickets-to-stay-unbeaten-ahead-of-crunch-england-match</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Captain Hayley Matthews and Stafanie Taylor lead the way for West Indies, who join England on six points atop Group B after five-wicket win in low-sco</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Fri, 19 Jun 2026 10</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>England's 2026 World Cup squad: All 26 players picked by Thomas Tuchel and why</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>espn_pw</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-06-22T06:26:25</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.espn.com/soccer/story/_/id/48823863/england-2026-world-cup-squad-26-players-picked-thomas-tuchel-why</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ESPN takes a look at every player named in the England squad for the 2026 World Cup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tuchel not afraid to shout at players - Watkins</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-06-21T22:04:05</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cjegy048847o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Thomas Tuchel has been in charge of England since January 2025  Ollie Watkins has said Thomas Tuchel is "not afraid" to shout at England players as th</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>England's Ollie Watkins on his World Cup role: 'It can be better to be a substitute than to start'</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>espn_pw</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-06-21T20:56:23</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.espn.com/soccer/story/_/id/49137379/england-ollie-watkins-world-cup-role-better-substitute-start</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>England striker Ollie Watkins has said he thinks his World Cup moment could be just around the corner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>The World Cup records that look set to be broken</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-06-21T13:55:05</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ghana at the World Cup 2026: Team Guide — History, Style, Players &amp; Group L</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>kickoff</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://kickoff.guide/blog/ghana-world-cup-2026-guide</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A team profile of Ghana (Black Stars) at the FIFA World Cup 2026: 74th in the FIFA ranking, 5th appearance, best result the 2010 quarter-finals, Otto </t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>England at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>kickoff</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://kickoff.guide/blog/england-world-cup-2026-guide</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>A team profile of England (Three Lions) at the FIFA World Cup 2026: 4th in the FIFA ranking, 17th appearance, one title in 1966, Thomas Tuchel's tacti</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>邮报：皮克福德为妻子准备纪念日惊喜</t>
+          <t>World Cup 2026: England boss Thomas Tuchel on how he has given his attackers freedom on the pitch</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>skysports</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-22 00:40</t>
+          <t>Tue, 23 Jun 2026 00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955719.html</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>https://www.skysports.com/football/news/12040/13556912/world-cup-2026-england-boss-thomas-tuchel-on-how-he-has-given-his-attackers-freedom-on-the-pitch</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>England's attack impressed in their World Cup opener against Croatia, scoring four goals; Ahead of their game with Ghana, Three Lions boss Thomas Tuch</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bukayo Saka returns to England training after individual session on Saturday</t>
+          <t>Has a World Cup game ever been abandoned before?</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-21T21:33:24</t>
+          <t>Tue, 23 Jun 2026 00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49137642/bukayo-saka-returns-england-training-individual-session-saturday</t>
+          <t>https://www.fourfourtwo.com/competition/has-a-world-cup-game-ever-been-abandoned-before</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bukayo Saka trained on Sunday ahead of England's World Cup clash with Ghana on Tuesday.</t>
+          <t>France vs Iraq at the 2026 World Cup kicked off at 9pm British time this evening, with Kylian Mbappe scoring the first half's only goal.  The Real Mad</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>丹-伯恩：贝林厄姆能够奠定基调，他有能给你带来能量的特质</t>
+          <t>From Times Square to England squad: Trevoh Chalobah realises World Cup dream</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-21 05:22</t>
+          <t>Sun, 21 Jun 2026 18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953477.html</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>https://www.theguardian.com/football/2026/jun/21/from-times-square-to-england-squad-trevoh-chalobah-realises-world-cup-dream</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Chelsea defender has mad scramble for boots and cuts short holiday after belatedly receiving the message of a lifetime from Thomas Tuchel  T revoh Cha</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 13</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thomas Partey in spotlight as he faces England and former Arsenal teammates after rape charges</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 11</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/thomas-partey-england-ghana-handshake</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ghana midfielder has denied all accusations as he prepares to begin his World Cup campaign in Boston on Tuesday  T he Football Association has remaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>England offer rare peek behind the curtain with no place to hide under Tuchel</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/england-world-cup-training-intensity-peek-behind-curtain-thomas-tuchel</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">There was more insight at the World Cup training base than usual with intensity on the rise under Thomas Tuchel  T he tall hooded figure kept barking </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sun Jun 21 2026 15:</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Women’s T20 World Cup: West Indies defeat Sri Lanka by five wickets to stay unbeaten ahead of crunch England match</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/cricket/news/12040/13556291/womens-t20-world-cup-west-indies-defeat-sri-lanka-by-five-wickets-to-stay-unbeaten-ahead-of-crunch-england-match</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Captain Hayley Matthews and Stafanie Taylor lead the way for West Indies, who join England on six points atop Group B after five-wicket win in low-sco</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fri, 19 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>England coach Tuchel wary of disturbing 'the music' at World Cup</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-23T00:22:40</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49148288/england-coach-tuchel-wary-disturbing-music-world-cup</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thomas Tuchel said his plan to ensure England's attacking players continue to thrive at the World Cup is to "not disturb the music" when they take on </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Why are England fans singing 'Wonderwall' at the World Cup?</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-22T16:36:29</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49144590/why-england-fans-singing-wonderwall-world-cup</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>It was one of the moments of the tournament so far. Why are England fans singing Wonderwall at the World Cup?</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Madueke's remarkable season - from petition to World Cup starter</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-22T10:47:17</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c5yz2xyvd1zo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Noni Madueke has made 12 appearances for England  When Noni Madueke was named in England's starting line-up for their World Cup opener against Croatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>England's 2026 World Cup squad: All 26 players picked by Thomas Tuchel and why</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-22T06:26:25</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/48823863/england-2026-world-cup-squad-26-players-picked-thomas-tuchel-why</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ESPN takes a look at every player named in the England squad for the 2026 World Cup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tuchel not afraid to shout at players - Watkins</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:04:05</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cjegy048847o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Thomas Tuchel has been in charge of England since January 2025  Ollie Watkins has said Thomas Tuchel is "not afraid" to shout at England players as th</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>England's Ollie Watkins on his World Cup role: 'It can be better to be a substitute than to start'</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-21T20:56:23</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49137379/england-ollie-watkins-world-cup-role-better-substitute-start</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>England striker Ollie Watkins has said he thinks his World Cup moment could be just around the corner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ghana at the World Cup 2026: Team Guide — History, Style, Players &amp; Group L</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/ghana-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A team profile of Ghana (Black Stars) at the FIFA World Cup 2026: 74th in the FIFA ranking, 5th appearance, best result the 2010 quarter-finals, Otto </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>England at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/england-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>A team profile of England (Three Lions) at the FIFA World Cup 2026: 4th in the FIFA ranking, 17th appearance, one title in 1966, Thomas Tuchel's tacti</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>图赫尔警告英格兰球员：一张红牌就可能毁掉世界杯</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959056&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lawrence Ati-Zigi Injury: Late call for Tuesday</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/lawrence-ati-zigi-injury-late-call-for-tuesday-520553</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Ati-Zigi (groin) is a late call for Tuesday's match against England, according to manager Carlos Queiroz, per Owuraku Ampof</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Bukayo Saka Injury: Recovered from injury</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/bukayo-saka-injury-recovered-from-injury-520561</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Saka (Achilles) is available for Tuesday's contest versus Ghana as England manager Thomas Tuchel has confirmed "Bukayo is g</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>邮报：皮克福德为妻子准备纪念日惊喜</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:40</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955719.html</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bukayo Saka returns to England training after individual session on Saturday</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-06-21T21:33:24</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49137642/bukayo-saka-returns-england-training-individual-session-saturday</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Bukayo Saka trained on Sunday ahead of England's World Cup clash with Ghana on Tuesday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>丹-伯恩：贝林厄姆能够奠定基调，他有能给你带来能量的特质</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:22</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953477.html</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>2026-06-22 08:38</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
 对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>New Zealand vs Egypt FIFA World Cup 2026 Preview: Everything you need to know</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>2026-06-21T10:14:27</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/new-zealand-egypt-world-cup-preview/blt1ef9c540246b6832</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>GOAL brings you everything you need to know about New Zealand vs Egypt at the 2026 FIFA World Cup.
 New Zealand vs Egypt will kick-off on 21 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>How does qualification for the World Cup knockout stage work?</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>2026-06-20T16:24:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
         </is>
@@ -1970,7 +2577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2008,30 +2615,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>克罗地亚国家队队长卢卡·莫德里奇将在对阵巴拿马的...</t>
+          <t>Panama vs Croatia Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-21 22:58</t>
+          <t>2026-06-22T11:39:12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955540.html</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/panama-vs-croatia-prediction-world-cup-2026-match-preview</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Both teams need to bounce back from opening defeats at the FIFA World Cup. We look ahead to Wednesday’s Group L clash with our Panama vs Croatia predi</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>官方：加蓬裁判阿乔将执法世界杯巴拿马vs克罗地亚</t>
+          <t>克罗地亚国家队队长卢卡·莫德里奇将在对阵巴拿马的...</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2041,12 +2652,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-21 01:49</t>
+          <t>2026-06-21 22:58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953239.html</t>
+          <t>https://www.dongqiudi.com/articles/5955540.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -2054,52 +2665,129 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
+          <t>官方：加蓬裁判阿乔将执法世界杯巴拿马vs克罗地亚</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fri, 19 Jun 2026 10</t>
+          <t>2026-06-21 01:49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953239.html</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Thomas Tuchel urges England to improve defence against Ghana after ‘wake-up call’</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/23/thomas-tuchel-england-ghana-world-cup-defence-improve</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Win over Ghana could secure top spot in the group  ‘We dropped too deep,’ Tuchel says of Croatia opener  Thomas Tuchel believes England were given a w</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>England World Cup latest: Thomas Tuchel set to leave it late to name XI to face Ghana on Tuesday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/news/12040/13556853/england-world-cup-latest-thomas-tuchel-set-to-leave-it-late-to-name-xi-to-face-ghana-on-tuesday</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sky Sports News' Rob Dorsett explains why Thomas Tuchel delays telling his England players if they are starting and looks at the selection dilemmas th</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fri, 19 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>England vs Ghana: predictions, best bets, stats and odds</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>8 minutes ago</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-predictions-betting-tips/</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">No previous meetings between these teams.
 No price boosts for this event.
@@ -2109,105 +2797,132 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>England vs Ghana team news and predicted lineups</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>squawka</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>44 minutes ago</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-team-news-predicted-lineups/</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>England will look to seal their place in the knockout stages when they face Ghana in Group L at the 2026 World Cup on Tuesday. Kick-off is scheduled f</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saka trains with England squad before Ghana match</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-06-22T00:13:38</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/c8e21d5w0pjo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Bukayo Saka (right) trained with the England squad on Sunday  Bukayo Saka has trained with the England squad to provide a fitness boost to Thomas Tuch</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>克罗地亚前锋穆萨：能在熟悉的达拉斯打入世界杯首球很不可思议</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-06-20 01:56</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5950333.html</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>England vs Ghana team news and predicted lineups</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>44 minutes ago</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-team-news-predicted-lineups/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>England will look to seal their place in the knockout stages when they face Ghana in Group L at the 2026 World Cup on Tuesday. Kick-off is scheduled f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Madueke's remarkable season - from petition to World Cup starter</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-22T10:47:17</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c5yz2xyvd1zo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Noni Madueke has made 12 appearances for England  When Noni Madueke was named in England's starting line-up for their World Cup opener against Croatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saka trains with England squad before Ghana match</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:13:38</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c8e21d5w0pjo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bukayo Saka (right) trained with the England squad on Sunday  Bukayo Saka has trained with the England squad to provide a fitness boost to Thomas Tuch</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>克罗地亚前锋穆萨：能在熟悉的达拉斯打入世界杯首球很不可思议</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-20 01:56</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5950333.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>England v Ghana: Live stream, team news, tickets and more</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2026-06-18T07:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/england-ghana-preview-live-stream-team-news-tickets</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>This is a modal window.
 Europe and Africa go head-to-head at Boston Stadium when England and Ghana meet in their second Group L fixture.
@@ -2215,255 +2930,333 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Panama at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>kickoff</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://kickoff.guide/blog/panama-world-cup-2026-guide</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">A team profile of Panama (La Marea Roja) at the FIFA World Cup 2026: 33rd in the FIFA ranking, 2nd appearance, Thomas Christiansen's tactics, players </t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Croatia at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>kickoff</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://kickoff.guide/blog/croatia-world-cup-2026-guide</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>A team profile of Croatia (Vatreni) at the FIFA World Cup 2026: 11th in the FIFA ranking, 7th appearance, 2018 runners-up, Zlatko Dalic's tactics, Luk</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Adalberto Carrasquilla Injury: Could be available Tuesday</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>rotowire</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://www.rotowire.com/soccer/headlines/adalberto-carrasquilla-injury-could-be-available-tuesday-520478</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Written by RotoWire Staff
 Carrasquilla (groin) returned to the training pitch Sunday but continues to train partially ahead of Tuesday's clash agains</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Adalberto Carrasquilla Injury: Suffers setback, out Tuesday</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/adalberto-carrasquilla-injury-suffers-setback-out-tuesday-520552</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Carrasquilla (groin) is out for Tuesday's match against Croatia, according to manager Thomas Christiansen, per Guillermo Pi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>苏契奇：适应国米对我不是问题；很难达到莫德里奇的高度</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>dongqiudi_team</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>2026-06-22 02:49</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/articles/5955931.html</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>World Cup 2026: England boss Thomas Tuchel on how he has given his attackers freedom on the pitch</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/news/12040/13556912/world-cup-2026-england-boss-thomas-tuchel-on-how-he-has-given-his-attackers-freedom-on-the-pitch</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>England's attack impressed in their World Cup opener against Croatia, scoring four goals; Ahead of their game with Ghana, Three Lions boss Thomas Tuch</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tuchel’s brash Britpop football is music to England ears before Ghana test</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/23/thomas-tuchel-britpop-football-england-world-cup-ghana</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Vinyl has baffled youngsters at the team’s hotel but spells of opening victory against Croatia showed side in the groove  I nside the foyer of the Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2026-06-22 08:38</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
 对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>The World Cup records that look set to be broken</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2026-06-21T13:55:05</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>New Zealand vs Egypt FIFA World Cup 2026 Preview: Everything you need to know</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2026-06-21T10:14:27</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/new-zealand-egypt-world-cup-preview/blt1ef9c540246b6832</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>GOAL brings you everything you need to know about New Zealand vs Egypt at the 2026 FIFA World Cup.
 New Zealand vs Egypt will kick-off on 21 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>How does qualification for the World Cup knockout stage work?</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2026-06-20T16:24:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Ghana at the World Cup 2026: Team Guide — History, Style, Players &amp; Group L</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>kickoff</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://kickoff.guide/blog/ghana-world-cup-2026-guide</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">A team profile of Ghana (Black Stars) at the FIFA World Cup 2026: 74th in the FIFA ranking, 5th appearance, best result the 2010 quarter-finals, Otto </t>
         </is>
@@ -2480,7 +3273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2518,169 +3311,173 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Colombia vs DR Congo Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-22T11:43:48</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/colombia-vs-dr-congo-prediction-world-cup-2026-match-preview</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>After holding heavyweights Portugal to a brave draw in their tournament opener, can DR Congo pull off another upset? Look ahead to Wednesday's FIFA Wo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Houston Rockets' Clint Capela dunks on DR Congo's footballers during FIFA World Cup visit</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-22T19:54:49</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/espn/story/_/id/49146131/houston-rockets-clint-capela-dunks-dr-congo-footballers-fifa-world-cup-visit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The Leopards, who have the World Cup base camp in Houston, spent part of their weekend visiting the Houston Rockets' training facility, where they wer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2026-06-21T18:22:43</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
 The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2026-06-21T17:04:43</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-06-21T16:35:30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
 The 2026 FIFA World Cup has completely ta</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-06-21T16:11:53</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>官方：意大利裁判马里亚尼将执法世界杯哥伦比亚vs民主刚果</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-21 01:51</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5953241.html</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>The Oldest Players in World Cup History</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-06-20T19:09:14</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/oldest-players-in-world-cup-history/</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Age is just a number for some footballers. Some even play the game on the grandest stage of all just before the end of their career. Here, we chart th</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>哥伦比亚第一人，路易斯-迪亚斯在世界杯首秀传射建功</t>
+          <t>官方：意大利裁判马里亚尼将执法世界杯哥伦比亚vs民主刚果</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2690,12 +3487,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-19 02:48</t>
+          <t>2026-06-21 01:51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5947469.html</t>
+          <t>https://www.dongqiudi.com/articles/5953241.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -2703,25 +3500,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>The Oldest Players in World Cup History</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-20T19:09:14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/oldest-players-in-world-cup-history/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Age is just a number for some footballers. Some even play the game on the grandest stage of all just before the end of their career. Here, we chart th</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>哥伦比亚第一人，路易斯-迪亚斯在世界杯首秀传射建功</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-19 02:48</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5947469.html</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Portugal vs Uzbekistan: predictions, best bets, stats and odds</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2 hours ago</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/portugal-vs-uzbekistan-predictions-tips/</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">No previous meetings between these teams.
 No price boosts for this event.
@@ -2731,180 +3578,180 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DR Congo at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>kickoff</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://kickoff.guide/blog/congo-dr-world-cup-2026-guide</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>A team profile of DR Congo (Leopards), back at the FIFA World Cup after 52 years: 46th in the FIFA ranking, 2nd appearance (as Zaire in 1974), Sebasti</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Colombia at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>kickoff</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://kickoff.guide/blog/colombia-world-cup-2026-guide</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A team profile of Colombia (Los Cafeteros) at the FIFA World Cup 2026: 13th in the FIFA ranking, 7th appearance, best result the 2014 quarter-finals, </t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bracketology: predict a path to World Cup victory</t>
+          <t>DR Congo at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Thu, 04 Jun 2026 10</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+          <t>https://kickoff.guide/blog/congo-dr-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+          <t>A team profile of DR Congo (Leopards), back at the FIFA World Cup after 52 years: 46th in the FIFA ranking, 2nd appearance (as Zaire in 1974), Sebasti</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Colombia at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/colombia-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A team profile of Colombia (Los Cafeteros) at the FIFA World Cup 2026: 13th in the FIFA ranking, 7th appearance, best result the 2014 quarter-finals, </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bracketology: predict a path to World Cup victory</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2026-06-22 08:38</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
 对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>How does qualification for the World Cup knockout stage work?</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>2026-06-20T16:24:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Uzbekistan at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>kickoff</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://kickoff.guide/blog/uzbekistan-world-cup-2026-guide</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>A team profile of Uzbekistan, who reached a first-ever FIFA World Cup: 50th in the FIFA ranking, coached by Italy's World Cup-winning captain Fabio Ca</t>
         </is>

--- a/data/worldcup_0624_0623update.xlsx
+++ b/data/worldcup_0624_0623update.xlsx
@@ -1287,7 +1287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2083,34 +2083,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>England coach Tuchel wary of disturbing 'the music' at World Cup</t>
+          <t>England boss Tuchel not a fan of hydration breaks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-23T00:22:40</t>
+          <t>2026-06-23T01:39:34</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49148288/england-coach-tuchel-wary-disturbing-music-world-cup</t>
+          <t>https://www.bbc.com/sport/football/articles/c4gyzknng1jo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Tuchel said his plan to ensure England's attacking players continue to thrive at the World Cup is to "not disturb the music" when they take on </t>
+          <t>Thomas Tuchel won all eight of their World Cup qualifiers without conceding a goal  England head coach Thomas Tuchel has admitted he is not a fan of t</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Why are England fans singing 'Wonderwall' at the World Cup?</t>
+          <t>England coach Tuchel wary of disturbing 'the music' at World Cup</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2120,182 +2120,186 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-22T16:36:29</t>
+          <t>2026-06-23T00:22:40</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49144590/why-england-fans-singing-wonderwall-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49148288/england-coach-tuchel-wary-disturbing-music-world-cup</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>It was one of the moments of the tournament so far. Why are England fans singing Wonderwall at the World Cup?</t>
+          <t xml:space="preserve">Thomas Tuchel said his plan to ensure England's attacking players continue to thrive at the World Cup is to "not disturb the music" when they take on </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Madueke's remarkable season - from petition to World Cup starter</t>
+          <t>Why are England fans singing 'Wonderwall' at the World Cup?</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-22T10:47:17</t>
+          <t>2026-06-22T16:36:29</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c5yz2xyvd1zo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.espn.com/soccer/story/_/id/49144590/why-england-fans-singing-wonderwall-world-cup</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Noni Madueke has made 12 appearances for England  When Noni Madueke was named in England's starting line-up for their World Cup opener against Croatia</t>
+          <t>It was one of the moments of the tournament so far. Why are England fans singing Wonderwall at the World Cup?</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>England's 2026 World Cup squad: All 26 players picked by Thomas Tuchel and why</t>
+          <t>Madueke's remarkable season - from petition to World Cup starter</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-22T06:26:25</t>
+          <t>2026-06-22T10:47:17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48823863/england-2026-world-cup-squad-26-players-picked-thomas-tuchel-why</t>
+          <t>https://www.bbc.com/sport/football/articles/c5yz2xyvd1zo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ESPN takes a look at every player named in the England squad for the 2026 World Cup.</t>
+          <t>Noni Madueke has made 12 appearances for England  When Noni Madueke was named in England's starting line-up for their World Cup opener against Croatia</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tuchel not afraid to shout at players - Watkins</t>
+          <t>England's 2026 World Cup squad: All 26 players picked by Thomas Tuchel and why</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-21T22:04:05</t>
+          <t>2026-06-22T06:26:25</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cjegy048847o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.espn.com/soccer/story/_/id/48823863/england-2026-world-cup-squad-26-players-picked-thomas-tuchel-why</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has been in charge of England since January 2025  Ollie Watkins has said Thomas Tuchel is "not afraid" to shout at England players as th</t>
+          <t>ESPN takes a look at every player named in the England squad for the 2026 World Cup.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>England's Ollie Watkins on his World Cup role: 'It can be better to be a substitute than to start'</t>
+          <t>Tuchel not afraid to shout at players - Watkins</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-21T20:56:23</t>
+          <t>2026-06-21T22:04:05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49137379/england-ollie-watkins-world-cup-role-better-substitute-start</t>
+          <t>https://www.bbc.com/sport/football/articles/cjegy048847o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>England striker Ollie Watkins has said he thinks his World Cup moment could be just around the corner.</t>
+          <t>Thomas Tuchel has been in charge of England since January 2025  Ollie Watkins has said Thomas Tuchel is "not afraid" to shout at England players as th</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The World Cup records that look set to be broken</t>
+          <t>England's Ollie Watkins on his World Cup role: 'It can be better to be a substitute than to start'</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-21T13:55:05</t>
+          <t>2026-06-21T20:56:23</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.espn.com/soccer/story/_/id/49137379/england-ollie-watkins-world-cup-role-better-substitute-start</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+          <t>England striker Ollie Watkins has said he thinks his World Cup moment could be just around the corner.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ghana at the World Cup 2026: Team Guide — History, Style, Players &amp; Group L</t>
+          <t>The World Cup records that look set to be broken</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>kickoff</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://kickoff.guide/blog/ghana-world-cup-2026-guide</t>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">A team profile of Ghana (Black Stars) at the FIFA World Cup 2026: 74th in the FIFA ranking, 5th appearance, best result the 2010 quarter-finals, Otto </t>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>England at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+          <t>Ghana at the World Cup 2026: Team Guide — History, Style, Players &amp; Group L</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2306,261 +2310,284 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://kickoff.guide/blog/england-world-cup-2026-guide</t>
+          <t>https://kickoff.guide/blog/ghana-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>A team profile of England (Three Lions) at the FIFA World Cup 2026: 4th in the FIFA ranking, 17th appearance, one title in 1966, Thomas Tuchel's tacti</t>
+          <t xml:space="preserve">A team profile of Ghana (Black Stars) at the FIFA World Cup 2026: 74th in the FIFA ranking, 5th appearance, best result the 2010 quarter-finals, Otto </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>图赫尔警告英格兰球员：一张红牌就可能毁掉世界杯</t>
+          <t>England at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
+          <t>kickoff</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959056&amp;from=tab_253</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>https://kickoff.guide/blog/england-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>A team profile of England (Three Lions) at the FIFA World Cup 2026: 4th in the FIFA ranking, 17th appearance, one title in 1966, Thomas Tuchel's tacti</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lawrence Ati-Zigi Injury: Late call for Tuesday</t>
+          <t>图赫尔警告英格兰球员：一张红牌就可能毁掉世界杯</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>rotowire</t>
+          <t>dongqiudi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959056&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Lawrence Ati-Zigi Injury: Late call for Tuesday</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>https://www.rotowire.com/soccer/headlines/lawrence-ati-zigi-injury-late-call-for-tuesday-520553</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Written by RotoWire Staff
 Ati-Zigi (groin) is a late call for Tuesday's match against England, according to manager Carlos Queiroz, per Owuraku Ampof</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Bukayo Saka Injury: Recovered from injury</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>rotowire</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>https://www.rotowire.com/soccer/headlines/bukayo-saka-injury-recovered-from-injury-520561</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Written by RotoWire Staff
 Saka (Achilles) is available for Tuesday's contest versus Ghana as England manager Thomas Tuchel has confirmed "Bukayo is g</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>邮报：皮克福德为妻子准备纪念日惊喜</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:40</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955719.html</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-    </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bukayo Saka returns to England training after individual session on Saturday</t>
+          <t>邮报：皮克福德为妻子准备纪念日惊喜</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-06-21T21:33:24</t>
+          <t>2026-06-22 00:40</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49137642/bukayo-saka-returns-england-training-individual-session-saturday</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Bukayo Saka trained on Sunday ahead of England's World Cup clash with Ghana on Tuesday.</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955719.html</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>丹-伯恩：贝林厄姆能够奠定基调，他有能给你带来能量的特质</t>
+          <t>Bukayo Saka returns to England training after individual session on Saturday</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-06-21 05:22</t>
+          <t>2026-06-21T21:33:24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953477.html</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49137642/bukayo-saka-returns-england-training-individual-session-saturday</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Bukayo Saka trained on Sunday ahead of England's World Cup clash with Ghana on Tuesday.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>丹-伯恩：贝林厄姆能够奠定基调，他有能给你带来能量的特质</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:22</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953477.html</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>2026-06-22 08:38</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
 对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>New Zealand vs Egypt FIFA World Cup 2026 Preview: Everything you need to know</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>2026-06-21T10:14:27</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/new-zealand-egypt-world-cup-preview/blt1ef9c540246b6832</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>GOAL brings you everything you need to know about New Zealand vs Egypt at the 2026 FIFA World Cup.
 New Zealand vs Egypt will kick-off on 21 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>How does qualification for the World Cup knockout stage work?</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2026-06-20T16:24:00</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
         </is>
@@ -2577,7 +2604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3132,131 +3159,158 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>England boss Tuchel not a fan of hydration breaks</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:39:34</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c4gyzknng1jo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Thomas Tuchel won all eight of their World Cup qualifiers without conceding a goal  England head coach Thomas Tuchel has admitted he is not a fan of t</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2026-06-22 08:38</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
 对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>The World Cup records that look set to be broken</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-06-21T13:55:05</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>New Zealand vs Egypt FIFA World Cup 2026 Preview: Everything you need to know</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2026-06-21T10:14:27</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/new-zealand-egypt-world-cup-preview/blt1ef9c540246b6832</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>GOAL brings you everything you need to know about New Zealand vs Egypt at the 2026 FIFA World Cup.
 New Zealand vs Egypt will kick-off on 21 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>How does qualification for the World Cup knockout stage work?</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-06-20T16:24:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Ghana at the World Cup 2026: Team Guide — History, Style, Players &amp; Group L</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>kickoff</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://kickoff.guide/blog/ghana-world-cup-2026-guide</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">A team profile of Ghana (Black Stars) at the FIFA World Cup 2026: 74th in the FIFA ranking, 5th appearance, best result the 2010 quarter-finals, Otto </t>
         </is>
